--- a/Assets/Excel/MapData.xlsx
+++ b/Assets/Excel/MapData.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18285" windowHeight="10275"/>
+    <workbookView windowWidth="18600" windowHeight="5850"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MapData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -58,6 +58,12 @@
     <t>taskGroupNum</t>
   </si>
   <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>buildTypeList</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t>List&lt;int&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">int </t>
+  </si>
+  <si>
     <t>地图编号</t>
   </si>
   <si>
@@ -94,6 +103,12 @@
     <t>任务组数</t>
   </si>
   <si>
+    <t>价格倍率</t>
+  </si>
+  <si>
+    <t>地图中的新设施</t>
+  </si>
+  <si>
     <t>春晖谷</t>
   </si>
   <si>
@@ -103,6 +118,9 @@
     <t>1,3</t>
   </si>
   <si>
+    <t>4,6,1</t>
+  </si>
+  <si>
     <t>碧澜谷</t>
   </si>
   <si>
@@ -112,16 +130,25 @@
     <t>1,2,3,4,5,6,7,8</t>
   </si>
   <si>
+    <t>8,3,2</t>
+  </si>
+  <si>
     <t>金露谷</t>
   </si>
   <si>
     <t>10,11,12,13,14,15,16,17,18,19,20,21,31</t>
   </si>
   <si>
+    <t>10,12,19</t>
+  </si>
+  <si>
     <t>云汀谷</t>
   </si>
   <si>
     <t>22,23,24,25,26,27,31,32,33,37</t>
+  </si>
+  <si>
+    <t>14,16</t>
   </si>
   <si>
     <t>望舒谷</t>
@@ -1061,7 +1088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="3" max="3" width="13.375" customWidth="1"/>
@@ -1071,9 +1098,10 @@
     <col min="7" max="7" width="21.125" customWidth="1"/>
     <col min="8" max="8" width="11.25" customWidth="1"/>
     <col min="9" max="9" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,71 +1129,89 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1174,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -1188,13 +1234,19 @@
       <c r="I4" s="1">
         <v>10</v>
       </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:11">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -1203,10 +1255,10 @@
         <v>15000</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -1217,13 +1269,19 @@
       <c r="I5" s="1">
         <v>20</v>
       </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -1232,10 +1290,10 @@
         <v>150000</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -1246,13 +1304,19 @@
       <c r="I6" s="1">
         <v>18</v>
       </c>
+      <c r="J6" s="1">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:11">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -1261,10 +1325,10 @@
         <v>300000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1275,13 +1339,19 @@
       <c r="I7" s="1">
         <v>20</v>
       </c>
+      <c r="J7" s="1">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
         <v>30</v>
@@ -1290,10 +1360,10 @@
         <v>500000</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="G8" s="1">
         <v>5</v>
@@ -1303,6 +1373,9 @@
       </c>
       <c r="I8" s="1">
         <v>22</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/MapData.xlsx
+++ b/Assets/Excel/MapData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18600" windowHeight="5850"/>
+    <workbookView windowWidth="24360" windowHeight="5850"/>
   </bookViews>
   <sheets>
     <sheet name="MapData" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>buildTypeList</t>
   </si>
   <si>
+    <t>monsterFamilyList</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>地图中的新设施</t>
   </si>
   <si>
+    <t>地图中拥有的怪物种类</t>
+  </si>
+  <si>
     <t>春晖谷</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>4,6,1</t>
   </si>
   <si>
+    <t>1,2</t>
+  </si>
+  <si>
     <t>碧澜谷</t>
   </si>
   <si>
@@ -133,28 +142,40 @@
     <t>8,3,2</t>
   </si>
   <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
     <t>金露谷</t>
   </si>
   <si>
-    <t>10,11,12,13,14,15,16,17,18,19,20,21,31</t>
+    <t>10,11,12,13,14,15,16,17,18,19,20,21,31,32</t>
   </si>
   <si>
     <t>10,12,19</t>
   </si>
   <si>
+    <t>4,5,6,7,11</t>
+  </si>
+  <si>
     <t>云汀谷</t>
   </si>
   <si>
-    <t>22,23,24,25,26,27,31,32,33,37</t>
+    <t>22,23,24,25,26,27,31,32,33,34,35,36,37,38</t>
   </si>
   <si>
     <t>14,16</t>
   </si>
   <si>
+    <t>8,9,11,12,13</t>
+  </si>
+  <si>
     <t>望舒谷</t>
   </si>
   <si>
-    <t>25,26,27,28,29,30,37,38,39,,40,41,42,43,44,45</t>
+    <t>25,26,27,28,29,30,37,38,39,40,41,42,43,44,45</t>
+  </si>
+  <si>
+    <t>9,10,13,14,15</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="3" max="3" width="13.375" customWidth="1"/>
@@ -1099,9 +1120,10 @@
     <col min="8" max="8" width="11.25" customWidth="1"/>
     <col min="9" max="9" width="15.375" customWidth="1"/>
     <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1132,86 +1154,95 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s">
-        <v>13</v>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
         <v>25</v>
       </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1220,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
@@ -1238,15 +1269,18 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -1255,10 +1289,10 @@
         <v>15000</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -1273,15 +1307,18 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -1290,10 +1327,10 @@
         <v>150000</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -1308,15 +1345,18 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -1325,10 +1365,10 @@
         <v>300000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1343,15 +1383,18 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1">
         <v>30</v>
@@ -1360,10 +1403,10 @@
         <v>500000</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>5</v>
@@ -1376,6 +1419,10 @@
       </c>
       <c r="J8" s="1">
         <v>10</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/MapData.xlsx
+++ b/Assets/Excel/MapData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24360" windowHeight="5850"/>
+    <workbookView windowWidth="21690" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="MapData" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -124,7 +124,7 @@
     <t>1,3</t>
   </si>
   <si>
-    <t>4,6,1</t>
+    <t>5,7</t>
   </si>
   <si>
     <t>1,2</t>
@@ -139,9 +139,6 @@
     <t>1,2,3,4,5,6,7,8</t>
   </si>
   <si>
-    <t>8,3,2</t>
-  </si>
-  <si>
     <t>1,2,3</t>
   </si>
   <si>
@@ -151,7 +148,7 @@
     <t>10,11,12,13,14,15,16,17,18,19,20,21,31,32</t>
   </si>
   <si>
-    <t>10,12,19</t>
+    <t>11,12</t>
   </si>
   <si>
     <t>4,5,6,7,11</t>
@@ -1306,11 +1303,11 @@
       <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5" t="s">
         <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1318,7 +1315,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -1327,7 +1324,7 @@
         <v>150000</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>35</v>
@@ -1345,10 +1342,10 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" t="s">
         <v>40</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1356,7 +1353,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -1365,7 +1362,7 @@
         <v>300000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>35</v>
@@ -1383,10 +1380,10 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
         <v>44</v>
-      </c>
-      <c r="L7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1394,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1">
         <v>30</v>
@@ -1403,7 +1400,7 @@
         <v>500000</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>35</v>
@@ -1420,9 +1417,8 @@
       <c r="J8" s="1">
         <v>10</v>
       </c>
-      <c r="K8"/>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
